--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486563_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486563_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.550700000000001</v>
+        <v>6.2723</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2159</v>
+        <v>4.9375</v>
       </c>
       <c r="F2" t="n">
         <v>1.3348</v>
@@ -610,10 +610,10 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1723</v>
+        <v>1.8939</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3864</v>
+        <v>1.108</v>
       </c>
       <c r="U2" t="n">
         <v>0.7859</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9568</v>
+        <v>3.8615</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1061</v>
+        <v>3.7334</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1493</v>
+        <v>0.1281</v>
       </c>
       <c r="G3" t="n">
         <v>1.5818</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.0424</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1706</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1491</v>
+        <v>0.1283</v>
       </c>
       <c r="V3" t="n">
         <v>1.017</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.114</v>
+        <v>2.3492</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6833</v>
+        <v>3.8261</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5693</v>
+        <v>-1.4768</v>
       </c>
       <c r="G4" t="n">
         <v>0.8249</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7279</v>
+        <v>0.5074</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9349</v>
+        <v>0.2079</v>
       </c>
       <c r="U4" t="n">
-        <v>0.207</v>
+        <v>0.2995</v>
       </c>
       <c r="V4" t="n">
         <v>1.017</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VAN ZEGEREN</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3578</v>
+        <v>0.5917</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1869</v>
+        <v>1.4336</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1709</v>
+        <v>-0.8418</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.49</v>
+        <v>-0.0989</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6111</v>
+        <v>0.2828</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1211</v>
+        <v>-0.3817</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0463</v>
+        <v>0.9777</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0302</v>
+        <v>0.7482</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0765</v>
+        <v>0.2295</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5364</v>
+        <v>-1.0767</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.581</v>
+        <v>-0.4654</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0446</v>
+        <v>-0.6112</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0431</v>
+        <v>-0.3061</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2281</v>
+        <v>-0.6741</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1851</v>
+        <v>0.368</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1952</v>
+        <v>-0.3082</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>-1.4382</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PAUKSTÈ</t>
+          <t>T. NASPLER PERAIRE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2916</v>
+        <v>0.4628</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6031</v>
+        <v>0.0411</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3115</v>
+        <v>0.4217</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.531</v>
+        <v>-0.3135</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2038</v>
+        <v>-0.5716</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7347</v>
+        <v>0.2582</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1695</v>
+        <v>0.8078</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0547</v>
+        <v>0.0428</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1147</v>
+        <v>0.765</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7004</v>
+        <v>-1.1213</v>
       </c>
       <c r="N6" t="n">
-        <v>0.149</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8495</v>
+        <v>-0.5068</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>1.735</v>
+        <v>0.1238</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4336</v>
+        <v>0.3209</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3014</v>
+        <v>-0.1971</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. NASPLER PERAIRE</t>
+          <t>J. PERIS CRESPO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,31 +955,31 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1593</v>
+        <v>0.3974</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1391</v>
+        <v>1.6109</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2984</v>
+        <v>-1.2135</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3135</v>
+        <v>0.1105</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5716</v>
+        <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2582</v>
+        <v>-0.0629</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8078</v>
+        <v>1.2318</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0428</v>
+        <v>0.7879</v>
       </c>
       <c r="L7" t="n">
-        <v>0.765</v>
+        <v>0.4439</v>
       </c>
       <c r="M7" t="n">
         <v>-1.1213</v>
@@ -991,37 +991,37 @@
         <v>-0.5068</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1798</v>
+        <v>0.307</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1406</v>
+        <v>0.1839</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3204</v>
+        <v>0.1232</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>J. VAN ZEGEREN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0047</v>
+        <v>-0.0207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8063</v>
+        <v>-0.1916</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8110000000000001</v>
+        <v>0.1709</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0989</v>
+        <v>-0.49</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2828</v>
+        <v>-0.6111</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3817</v>
+        <v>0.1211</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9777</v>
+        <v>0.0463</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7482</v>
+        <v>-0.0302</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2295</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0767</v>
+        <v>-0.5364</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4654</v>
+        <v>-0.581</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6112</v>
+        <v>0.0446</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9026</v>
+        <v>0.6645</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3014</v>
+        <v>0.8496</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3988</v>
+        <v>-0.1851</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3082</v>
+        <v>-0.1952</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4382</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PERIS CRESPO</t>
+          <t>J. ROUND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5468</v>
+        <v>-0.4027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6051</v>
+        <v>-0.6217</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1518</v>
+        <v>0.219</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1105</v>
+        <v>-1.1751</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1734</v>
+        <v>-1.25</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0629</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2318</v>
+        <v>-0.5208</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7879</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4439</v>
+        <v>0.1147</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1213</v>
+        <v>-0.6543</v>
       </c>
       <c r="N9" t="n">
         <v>-0.6143999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5068</v>
+        <v>-0.0399</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6371</v>
+        <v>-0.3151</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.822</v>
+        <v>-0.1009</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1848</v>
+        <v>-0.2142</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ROUND</t>
+          <t>J. PAUKSTÈ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8258</v>
+        <v>-0.5524</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1373</v>
+        <v>0.8208</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3115</v>
+        <v>-1.3732</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1751</v>
+        <v>-0.531</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.25</v>
+        <v>0.2038</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07489999999999999</v>
+        <v>-0.7347</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5208</v>
+        <v>0.1695</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.0547</v>
       </c>
       <c r="L10" t="n">
         <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6543</v>
+        <v>-0.7004</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6143999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0399</v>
+        <v>-0.8495</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7382</v>
+        <v>0.8911</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>0.6513</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1217</v>
+        <v>0.2397</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6288</v>
+        <v>-2.0392</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4281</v>
+        <v>-2.8693</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7993</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0156</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3904</v>
+        <v>0.1992</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4194</v>
+        <v>0.1394</v>
       </c>
       <c r="U11" t="n">
-        <v>0.029</v>
+        <v>0.0598</v>
       </c>
       <c r="V11" t="n">
         <v>1.2122</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.022</v>
+        <v>-3.833</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9437</v>
+        <v>-3.4773</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.3557</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3476</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7606</v>
+        <v>0.9496</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0347</v>
+        <v>0.5011</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7259</v>
+        <v>0.4485</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.402100000000001</v>
+        <v>7.086899999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>8.558500000000002</v>
+        <v>9.243499999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1563</v>
+        <v>-2.1564</v>
       </c>
       <c r="G13" t="n">
         <v>-4.4857</v>
@@ -1444,7 +1444,7 @@
         <v>7.0815</v>
       </c>
       <c r="K13" t="n">
-        <v>1.690499999999999</v>
+        <v>1.690500000000001</v>
       </c>
       <c r="L13" t="n">
         <v>5.3908</v>
@@ -1468,10 +1468,10 @@
         <v>13.0502</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1879</v>
+        <v>4.8729</v>
       </c>
       <c r="T13" t="n">
-        <v>2.331300000000001</v>
+        <v>3.016500000000001</v>
       </c>
       <c r="U13" t="n">
         <v>1.8565</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.391</v>
+        <v>6.5349</v>
       </c>
       <c r="E14" t="n">
         <v>6.7109</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3199</v>
+        <v>-0.176</v>
       </c>
       <c r="G14" t="n">
         <v>6.5843</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0667</v>
+        <v>0.2106</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2704</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3371</v>
+        <v>0.481</v>
       </c>
       <c r="V14" t="n">
         <v>-1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2298</v>
+        <v>2.7508</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1527</v>
+        <v>2.2645</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0771</v>
+        <v>0.4863</v>
       </c>
       <c r="G15" t="n">
         <v>3.7285</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6112</v>
+        <v>0.1322</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4759</v>
+        <v>-0.3641</v>
       </c>
       <c r="U15" t="n">
-        <v>1.087</v>
+        <v>0.4963</v>
       </c>
       <c r="V15" t="n">
         <v>0.1952</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1078</v>
+        <v>0.7605</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1233</v>
+        <v>2.1708</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0155</v>
+        <v>-1.4103</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9539</v>
+        <v>2.6985</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1044</v>
+        <v>1.8976</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.0583</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0103</v>
+        <v>3.6111</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4782</v>
+        <v>1.0069</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4885</v>
+        <v>2.6042</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9436</v>
+        <v>-0.9126</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6262</v>
+        <v>0.8907</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5698</v>
+        <v>-1.8033</v>
       </c>
       <c r="P16" t="n">
-        <v>0.87</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0122</v>
+        <v>-0.0544</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0036</v>
+        <v>0.1274</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0158</v>
+        <v>-0.1818</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2039</v>
+        <v>0.074</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.695</v>
       </c>
       <c r="X16" t="n">
-        <v>0.074</v>
+        <v>-1.621</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1733</v>
+        <v>0.6216</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0591</v>
+        <v>1.1233</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2323</v>
+        <v>-0.5017</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6985</v>
+        <v>-0.9539</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8976</v>
+        <v>2.1044</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8008999999999999</v>
+        <v>-3.0583</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6111</v>
+        <v>-0.0103</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0069</v>
+        <v>1.4782</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6042</v>
+        <v>-1.4885</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9126</v>
+        <v>-0.9436</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8907</v>
+        <v>0.6262</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8033</v>
+        <v>-1.5698</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9882</v>
+        <v>-0.4984</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0156</v>
+        <v>0.0036</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0038</v>
+        <v>-0.502</v>
       </c>
       <c r="V17" t="n">
+        <v>1.2039</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
         <v>0.074</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.695</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.621</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1862</v>
+        <v>-0.2337</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0405</v>
+        <v>0.0713</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1457</v>
+        <v>-0.3049</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3834</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1166</v>
+        <v>-0.164</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1935</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0769</v>
+        <v>-0.0823</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1213</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5018</v>
+        <v>-1.7074</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1607</v>
+        <v>-1.6077</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3412</v>
+        <v>-0.0997</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3972</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6474</v>
+        <v>-0.8529</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0769</v>
+        <v>-0.5239</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5705</v>
+        <v>-0.329</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7686</v>
+        <v>-1.7917</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3507</v>
+        <v>-3.1271</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5821</v>
+        <v>1.3355</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1384</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>0.13</v>
+        <v>0.1069</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4494</v>
       </c>
       <c r="U20" t="n">
-        <v>0.803</v>
+        <v>0.5564</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1952</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9722</v>
+        <v>-2.0236</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9352</v>
+        <v>0.4881</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9074</v>
+        <v>-2.5118</v>
       </c>
       <c r="G21" t="n">
         <v>-1.481</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3495</v>
+        <v>0.298</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.5191</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6167</v>
+        <v>-0.2211</v>
       </c>
       <c r="V21" t="n">
         <v>0.4644</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8918</v>
+        <v>-3.3909</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8914</v>
+        <v>-1.6679</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0004</v>
+        <v>-1.723</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0562</v>
@@ -2170,13 +2170,13 @@
         <v>0.2175</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4746</v>
+        <v>-0.9737</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.536</v>
+        <v>-0.3124</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9387</v>
+        <v>-0.6612</v>
       </c>
       <c r="V22" t="n">
         <v>-0.491</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6367</v>
+        <v>-6.4325</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3816</v>
+        <v>-4.2698</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2552</v>
+        <v>-2.1627</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1155</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1064</v>
+        <v>-0.9022</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4899</v>
+        <v>-0.3975</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3698</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.402000000000001</v>
+        <v>-4.912000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1563</v>
+        <v>2.156400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.558399999999999</v>
+        <v>-7.068300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>4.4857</v>
@@ -2326,13 +2326,13 @@
         <v>6.525</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.188</v>
+        <v>-2.6979</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.8567</v>
+        <v>-1.8565</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.3314</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1745999999999999</v>
